--- a/tools/importer/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-02-05T17:55:00.918Z</t>
+    <t>2026-02-05T18:32:59.007Z</t>
   </si>
   <si>
     <t>Wireless Broadband for First Responders and Public Safety | FirstNet</t>

--- a/tools/importer/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-02-05T18:32:59.007Z</t>
+    <t>2026-02-05T20:50:26.476Z</t>
   </si>
   <si>
     <t>Wireless Broadband for First Responders and Public Safety | FirstNet</t>
